--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13DA9A51-A1FE-4893-BC30-41303AACC3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1128AB0-9BF9-4627-9A61-722ACAD50F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="380" windowWidth="19180" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="57">
   <si>
     <t>project_name</t>
   </si>
@@ -58,51 +58,6 @@
     <t>בנק יהב</t>
   </si>
   <si>
-    <t>הגדרת דרישות מערכת</t>
-  </si>
-  <si>
-    <t>בניית אפיון טכני</t>
-  </si>
-  <si>
-    <t>בדיקות קבלה</t>
-  </si>
-  <si>
-    <t>הטמעת מודול דיווח</t>
-  </si>
-  <si>
-    <t>סקירת קוד ראשונית</t>
-  </si>
-  <si>
-    <t>העברה לסביבת ייצור</t>
-  </si>
-  <si>
-    <t>מיפוי תהליכים קיימים</t>
-  </si>
-  <si>
-    <t>פיתוח ממשק ניהול</t>
-  </si>
-  <si>
-    <t>הדרכת משתמשים</t>
-  </si>
-  <si>
-    <t>ניתוח פערים</t>
-  </si>
-  <si>
-    <t>אפיון מסכי דיווח</t>
-  </si>
-  <si>
-    <t>בדיקות מקצה לקצה</t>
-  </si>
-  <si>
-    <t>כתיבת מסמך דרישות</t>
-  </si>
-  <si>
-    <t>פיתוח שכבת אינטגרציה</t>
-  </si>
-  <si>
-    <t>בדיקות אבטחה</t>
-  </si>
-  <si>
     <t>הושלם</t>
   </si>
   <si>
@@ -112,40 +67,130 @@
     <t>ממתין</t>
   </si>
   <si>
-    <t>דנה כהן</t>
-  </si>
-  <si>
-    <t>רון לוי</t>
-  </si>
-  <si>
-    <t>מיכל ברק</t>
-  </si>
-  <si>
-    <t>יואב שמיר</t>
-  </si>
-  <si>
-    <t>אביב גל</t>
-  </si>
-  <si>
-    <t>ממתין לאישור לקוח</t>
-  </si>
-  <si>
-    <t>באיחור קל</t>
-  </si>
-  <si>
-    <t>תלוי בסיום הבדיקות</t>
-  </si>
-  <si>
-    <t>לתאם מול הלקוח</t>
-  </si>
-  <si>
-    <t>באיחור — נדרש מעקב</t>
-  </si>
-  <si>
-    <t>מורכבות גבוהה</t>
-  </si>
-  <si>
-    <t>חובה לפני העלייה לאוויר</t>
+    <t xml:space="preserve">אלישבע שליסל </t>
+  </si>
+  <si>
+    <t xml:space="preserve">העלאת גרסה בעמיתים לטסט </t>
+  </si>
+  <si>
+    <t>בדיקת גרסת עמיתים בטסטים</t>
+  </si>
+  <si>
+    <t>ורד גדנקן</t>
+  </si>
+  <si>
+    <t xml:space="preserve">יחד עם יעל </t>
+  </si>
+  <si>
+    <t xml:space="preserve">העלאת גרסת עמיתים לייצור </t>
+  </si>
+  <si>
+    <t xml:space="preserve">בהתאם לאישור לקוח </t>
+  </si>
+  <si>
+    <t xml:space="preserve">אנליסט </t>
+  </si>
+  <si>
+    <t>מתן שרון</t>
+  </si>
+  <si>
+    <t xml:space="preserve">באישור אבט"מ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">הטמעת PlayWright במערכות </t>
+  </si>
+  <si>
+    <t xml:space="preserve">אריק ישראל </t>
+  </si>
+  <si>
+    <t>כולל GUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">בביצוע </t>
+  </si>
+  <si>
+    <t xml:space="preserve">סתיו ברנשטיין </t>
+  </si>
+  <si>
+    <t>העברת תמחור לדף בית חדש בעמיתים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סיון פרידמן </t>
+  </si>
+  <si>
+    <t>הגדרת פתרון מאובטח לבעיית גישה בייצור</t>
+  </si>
+  <si>
+    <t>עבור ספי</t>
+  </si>
+  <si>
+    <t>תיאום תאריך העלאת גרסת משיכות בעמיתים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ממתין </t>
+  </si>
+  <si>
+    <t xml:space="preserve">אסתי רדליך </t>
+  </si>
+  <si>
+    <t xml:space="preserve">פרויקט משיכות </t>
+  </si>
+  <si>
+    <t>פיתוח תכולות גרסת תיקים בעמיתים</t>
+  </si>
+  <si>
+    <t>ביצוע משימות פתוחות ב-Azure DevOps</t>
+  </si>
+  <si>
+    <t>שושנה בלוי</t>
+  </si>
+  <si>
+    <t>פיתוח תשתיתי - מצב צפייה/קריאה בלבד באתר</t>
+  </si>
+  <si>
+    <t>ממתין לאפיון הלקוח</t>
+  </si>
+  <si>
+    <t>העברת בקשה להזמנה חדשה עבור הפיתוח</t>
+  </si>
+  <si>
+    <t xml:space="preserve">רעות מקדמת </t>
+  </si>
+  <si>
+    <t>ביצוע עדכונים בפתרון במסגרת תחזוקה שוטפת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">אנדריי שמיגול </t>
+  </si>
+  <si>
+    <t xml:space="preserve">תיעוד מסמכים בתיקיית רשת </t>
+  </si>
+  <si>
+    <t>מתבצע אחת לחודש/חודשיים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">קבלת גישה לכספת מול הבנק </t>
+  </si>
+  <si>
+    <t xml:space="preserve">נמסר לנתנאל </t>
+  </si>
+  <si>
+    <t xml:space="preserve">מעבר מסמך סקר אבטחת מידע </t>
+  </si>
+  <si>
+    <t>נתנאל אליפז</t>
+  </si>
+  <si>
+    <t>יש לבדוק האם במסגרת אחריותנו</t>
+  </si>
+  <si>
+    <t>מסירת תאריך לסקר חוזר</t>
+  </si>
+  <si>
+    <t>אלרן עקיבא</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ממתין לתשובת הסוקרים </t>
   </si>
 </sst>
 </file>
@@ -490,15 +535,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.58203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.9140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -529,19 +574,19 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
-        <v>27</v>
-      </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E2" s="1">
-        <v>46116</v>
+        <v>46156</v>
       </c>
       <c r="F2" s="1">
-        <v>46116</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -549,22 +594,22 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1">
-        <v>46117</v>
+        <v>46156</v>
       </c>
       <c r="F3" s="1">
-        <v>46117</v>
+        <v>46159</v>
       </c>
       <c r="G3" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -572,42 +617,45 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1">
-        <v>46118</v>
+        <v>46161</v>
       </c>
       <c r="F4" s="1">
-        <v>46118</v>
+        <v>46161</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E5" s="1">
-        <v>46119</v>
+        <v>46161</v>
       </c>
       <c r="F5" s="1">
-        <v>46119</v>
+        <v>46162</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -615,19 +663,22 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="1">
+        <v>46152</v>
+      </c>
+      <c r="F6" s="1">
+        <v>46166</v>
+      </c>
+      <c r="G6" t="s">
         <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="1">
-        <v>46120</v>
-      </c>
-      <c r="F6" s="1">
-        <v>46120</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -635,62 +686,65 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
         <v>29</v>
       </c>
-      <c r="D7" t="s">
-        <v>31</v>
-      </c>
       <c r="E7" s="1">
-        <v>46121</v>
+        <v>46105</v>
       </c>
       <c r="F7" s="1">
-        <v>46121</v>
-      </c>
-      <c r="G7" t="s">
-        <v>37</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E8" s="1">
-        <v>46122</v>
+        <v>46156</v>
       </c>
       <c r="F8" s="1">
-        <v>46122</v>
+        <v>46163</v>
+      </c>
+      <c r="G8" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E9" s="1">
-        <v>46123</v>
+        <v>46174</v>
       </c>
       <c r="F9" s="1">
-        <v>46123</v>
+        <v>46188</v>
+      </c>
+      <c r="G9" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -698,65 +752,65 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E10" s="1">
-        <v>46124</v>
+        <v>46146</v>
       </c>
       <c r="F10" s="1">
-        <v>46124</v>
-      </c>
-      <c r="G10" t="s">
-        <v>38</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E11" s="1">
-        <v>46125</v>
+        <v>46145</v>
       </c>
       <c r="F11" s="1">
-        <v>46125</v>
+        <v>46173</v>
+      </c>
+      <c r="G11" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E12" s="1">
-        <v>46126</v>
+        <v>46143</v>
       </c>
       <c r="F12" s="1">
-        <v>46126</v>
+        <v>46143</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -764,39 +818,42 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="E13" s="1">
-        <v>46127</v>
+        <v>46113</v>
       </c>
       <c r="F13" s="1">
-        <v>46127</v>
+        <v>46142</v>
+      </c>
+      <c r="G13" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E14" s="1">
-        <v>46128</v>
+        <v>46157</v>
       </c>
       <c r="F14" s="1">
-        <v>46128</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -804,22 +861,22 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E15" s="1">
-        <v>46129</v>
+        <v>46128</v>
       </c>
       <c r="F15" s="1">
         <v>46129</v>
       </c>
       <c r="G15" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -827,22 +884,45 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="E16" s="1">
-        <v>46130</v>
+        <v>46129</v>
       </c>
       <c r="F16" s="1">
-        <v>46130</v>
+        <v>46173</v>
       </c>
       <c r="G16" t="s">
-        <v>41</v>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" s="1">
+        <v>46174</v>
+      </c>
+      <c r="F17" s="1">
+        <v>46188</v>
+      </c>
+      <c r="G17" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1128AB0-9BF9-4627-9A61-722ACAD50F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5647665-3F39-4000-BEA9-BE88B52FA20D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="55">
   <si>
     <t>project_name</t>
   </si>
@@ -106,9 +106,6 @@
     <t>כולל GUI</t>
   </si>
   <si>
-    <t xml:space="preserve">בביצוע </t>
-  </si>
-  <si>
     <t xml:space="preserve">סתיו ברנשטיין </t>
   </si>
   <si>
@@ -125,9 +122,6 @@
   </si>
   <si>
     <t>תיאום תאריך העלאת גרסת משיכות בעמיתים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ממתין </t>
   </si>
   <si>
     <t xml:space="preserve">אסתי רדליך </t>
@@ -540,7 +534,7 @@
   <cols>
     <col min="1" max="1" width="11.58203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.5" customWidth="1"/>
     <col min="4" max="4" width="11.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9.75" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24.5" bestFit="1" customWidth="1"/>
@@ -640,7 +634,7 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
@@ -686,13 +680,13 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
         <v>28</v>
-      </c>
-      <c r="D7" t="s">
-        <v>29</v>
       </c>
       <c r="E7" s="1">
         <v>46105</v>
@@ -706,13 +700,13 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8" s="1">
         <v>46156</v>
@@ -721,7 +715,7 @@
         <v>46163</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -729,13 +723,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
         <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s">
-        <v>36</v>
       </c>
       <c r="E9" s="1">
         <v>46174</v>
@@ -744,7 +738,7 @@
         <v>46188</v>
       </c>
       <c r="G9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -752,13 +746,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E10" s="1">
         <v>46146</v>
@@ -772,13 +766,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E11" s="1">
         <v>46145</v>
@@ -787,7 +781,7 @@
         <v>46173</v>
       </c>
       <c r="G11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -795,13 +789,13 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E12" s="1">
         <v>46143</v>
@@ -810,7 +804,7 @@
         <v>46143</v>
       </c>
       <c r="G12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -818,13 +812,13 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E13" s="1">
         <v>46113</v>
@@ -833,7 +827,7 @@
         <v>46142</v>
       </c>
       <c r="G13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -841,13 +835,13 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E14" s="1">
         <v>46157</v>
@@ -861,13 +855,13 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E15" s="1">
         <v>46128</v>
@@ -876,7 +870,7 @@
         <v>46129</v>
       </c>
       <c r="G15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -884,13 +878,13 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E16" s="1">
         <v>46129</v>
@@ -899,7 +893,7 @@
         <v>46173</v>
       </c>
       <c r="G16" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -907,13 +901,13 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E17" s="1">
         <v>46174</v>
@@ -922,7 +916,7 @@
         <v>46188</v>
       </c>
       <c r="G17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
